--- a/data/raw/inventory/Week 19/Tonor/Inventory Snapshot.xlsx
+++ b/data/raw/inventory/Week 19/Tonor/Inventory Snapshot.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\Other computers\My Laptop\D\Nitesh\Weekly Report - B2B + B2C\FastAPI\data\raw\inventory\Week 19\Tonor\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B229737-03A0-4471-B410-CB8197C47F1C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{072C4DDC-9E02-4CD7-8FFC-2B36F4ADA122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{D49B0F4C-5F9E-467E-8AD9-9E638F42404F}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="123">
   <si>
     <t>SKU</t>
   </si>
@@ -403,6 +403,9 @@
   </si>
   <si>
     <t>YNT</t>
+  </si>
+  <si>
+    <t>Open Order</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1005,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}">
-  <dimension ref="A1:L97"/>
+  <dimension ref="A1:L100"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -2971,33 +2974,93 @@
       </c>
       <c r="K97" s="8"/>
     </row>
+    <row r="98" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="B98" s="1" t="s">
+        <v>47</v>
+      </c>
+      <c r="C98" t="s">
+        <v>113</v>
+      </c>
+      <c r="D98" s="1" t="s">
+        <v>74</v>
+      </c>
+      <c r="I98" s="1">
+        <v>30</v>
+      </c>
+      <c r="J98" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="B99" s="1" t="s">
+        <v>50</v>
+      </c>
+      <c r="C99" t="s">
+        <v>113</v>
+      </c>
+      <c r="D99" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="I99" s="1">
+        <v>80</v>
+      </c>
+      <c r="J99" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="C100" t="s">
+        <v>113</v>
+      </c>
+      <c r="D100" s="1" t="s">
+        <v>92</v>
+      </c>
+      <c r="I100" s="1">
+        <v>256</v>
+      </c>
+      <c r="J100" s="1" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:L97" xr:uid="{76CBFB1B-DC23-4380-8138-4D6BFF18CBC5}"/>
   <phoneticPr fontId="3" type="noConversion"/>
   <conditionalFormatting sqref="A59">
     <cfRule type="duplicateValues" dxfId="10" priority="11"/>
   </conditionalFormatting>
+  <conditionalFormatting sqref="A59:A91">
+    <cfRule type="duplicateValues" dxfId="9" priority="1587"/>
+  </conditionalFormatting>
   <conditionalFormatting sqref="A77:A79">
-    <cfRule type="duplicateValues" dxfId="9" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="13"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="A1:B1">
-    <cfRule type="duplicateValues" dxfId="7" priority="1353"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="1353"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D1:H1">
-    <cfRule type="duplicateValues" dxfId="6" priority="1564"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="1565" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="1564"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="1565" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="I1">
-    <cfRule type="duplicateValues" dxfId="4" priority="1351"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="1352" stopIfTrue="1"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="1351"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="1352" stopIfTrue="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="J1:L1">
-    <cfRule type="duplicateValues" dxfId="2" priority="1349"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="1350" stopIfTrue="1"/>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="A59:A91">
-    <cfRule type="duplicateValues" dxfId="0" priority="1587"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="1349"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="1350" stopIfTrue="1"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
